--- a/maps/map2.xlsx
+++ b/maps/map2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="A:\projects in programming\python\AgentStorage\AgentStorageDiplom\maps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{248DB544-ABF4-4F20-8CA7-5909ACA71D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4B87BF5-5348-4A1C-811E-C84B669DF7DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
